--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,52 +1251,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118326060</v>
+        <v>137016308</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>58008</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ljusmon, Ljusmon, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637736</v>
+        <v>637653</v>
       </c>
       <c r="R7" t="n">
-        <v>7012765</v>
+        <v>7012948</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,22 +1324,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,24 +1359,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118326060</t>
+          <t>https://artportalen.se/Sighting/137016308</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118326208</v>
+        <v>118326060</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1397,19 +1406,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sunnersta-Stormyran, Sunnersta-Stormyran, Ång</t>
+          <t>Ljusmon, Ljusmon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637768</v>
+        <v>637736</v>
       </c>
       <c r="R8" t="n">
-        <v>7012813</v>
+        <v>7012765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,13 +1486,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118326208</t>
+          <t>https://artportalen.se/Sighting/118326060</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118326344</v>
+        <v>118326208</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1513,19 +1522,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ljusmon, Ljusmon, Ång</t>
+          <t>Sunnersta-Stormyran, Sunnersta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637727</v>
+        <v>637768</v>
       </c>
       <c r="R9" t="n">
-        <v>7012895</v>
+        <v>7012813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,13 +1602,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118326344</t>
+          <t>https://artportalen.se/Sighting/118326208</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118326401</v>
+        <v>118326344</v>
       </c>
       <c r="B10" t="n">
         <v>99118</v>
@@ -1629,7 +1638,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1638,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637692</v>
+        <v>637727</v>
       </c>
       <c r="R10" t="n">
-        <v>7012939</v>
+        <v>7012895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,13 +1718,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118326401</t>
+          <t>https://artportalen.se/Sighting/118326344</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118511426</v>
+        <v>118326401</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1745,31 +1754,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Följansbodarna, S om, Ång</t>
+          <t>Ljusmon, Ljusmon, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637754</v>
+        <v>637692</v>
       </c>
       <c r="R11" t="n">
-        <v>7012806</v>
+        <v>7012939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,51 +1796,51 @@
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>SBF Florainventering i Ångermanland 2024</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118511426</t>
+          <t>https://artportalen.se/Sighting/118326401</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118511429</v>
+        <v>118511426</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1873,7 +1870,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1894,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637737</v>
+        <v>637754</v>
       </c>
       <c r="R12" t="n">
-        <v>7012765</v>
+        <v>7012806</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1962,390 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/118511426</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118511429</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Följansbodarna, S om, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>637737</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7012765</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/118511429</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137016309</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>637583</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7012906</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1150 plantor inom en cirka 10 meters radie.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016309</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137016310</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>637569</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7012874</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016310</t>
         </is>
       </c>
     </row>
@@ -1982,6 +2362,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -2099,7 +2099,7 @@
         <v>137016309</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137016310</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -2099,7 +2099,7 @@
         <v>137016309</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137016310</v>
       </c>
       <c r="B15" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -2099,7 +2099,7 @@
         <v>137016309</v>
       </c>
       <c r="B14" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137016310</v>
       </c>
       <c r="B15" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,52 +1135,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937707</v>
+        <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>OffersjÃ¶n, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637626</v>
+        <v>637874</v>
       </c>
       <c r="R6" t="n">
-        <v>7012930</v>
+        <v>7012654</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,22 +1203,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,74 +1229,81 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119937707</t>
+          <t>https://artportalen.se/Sighting/137124325</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137016308</v>
+        <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637653</v>
+        <v>637827</v>
       </c>
       <c r="R7" t="n">
-        <v>7012948</v>
+        <v>7012677</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1324,27 +1330,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,16 +1371,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016308</t>
+          <t>https://artportalen.se/Sighting/137124336</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118326060</v>
+        <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,41 +1388,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ljusmon, Ljusmon, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637736</v>
+        <v>637668</v>
       </c>
       <c r="R8" t="n">
-        <v>7012765</v>
+        <v>7012859</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,22 +1445,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,31 +1471,46 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118326060</t>
+          <t>https://artportalen.se/Sighting/137124349</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118326208</v>
+        <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,41 +1518,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sunnersta-Stormyran, Sunnersta-Stormyran, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637768</v>
+        <v>637663</v>
       </c>
       <c r="R9" t="n">
-        <v>7012813</v>
+        <v>7012817</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,22 +1575,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,31 +1601,46 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118326208</t>
+          <t>https://artportalen.se/Sighting/137124350</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118326344</v>
+        <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,41 +1648,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ljusmon, Ljusmon, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637727</v>
+        <v>637786</v>
       </c>
       <c r="R10" t="n">
-        <v>7012895</v>
+        <v>7012715</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,22 +1705,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,33 +1729,49 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118326344</t>
+          <t>https://artportalen.se/Sighting/137132734</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118326401</v>
+        <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,41 +1779,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ljusmon, Ljusmon, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637692</v>
+        <v>637774</v>
       </c>
       <c r="R11" t="n">
-        <v>7012939</v>
+        <v>7012708</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,22 +1836,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,33 +1860,49 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118326401</t>
+          <t>https://artportalen.se/Sighting/137132736</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118511426</v>
+        <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,53 +1910,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Följansbodarna, S om, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637754</v>
+        <v>637713</v>
       </c>
       <c r="R12" t="n">
-        <v>7012806</v>
+        <v>7012795</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,12 +1967,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,39 +1995,45 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>SBF Florainventering i Ångermanland 2024</t>
-        </is>
-      </c>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118511426</t>
+          <t>https://artportalen.se/Sighting/137132739</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118511429</v>
+        <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,53 +2041,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Följansbodarna, S om, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>637737</v>
+        <v>637677</v>
       </c>
       <c r="R13" t="n">
-        <v>7012765</v>
+        <v>7012839</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2049,12 +2098,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,39 +2126,45 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>SBF Florainventering i Ångermanland 2024</t>
-        </is>
-      </c>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118511429</t>
+          <t>https://artportalen.se/Sighting/137132746</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137016309</v>
+        <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>99362</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,35 +2172,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2143,13 +2199,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637583</v>
+        <v>637679</v>
       </c>
       <c r="R14" t="n">
-        <v>7012906</v>
+        <v>7012847</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2173,27 +2229,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1150 plantor inom en cirka 10 meters radie.</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,30 +2257,45 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016309</t>
+          <t>https://artportalen.se/Sighting/137132747</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137016310</v>
+        <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>99362</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,35 +2303,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2273,13 +2330,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637569</v>
+        <v>637677</v>
       </c>
       <c r="R15" t="n">
-        <v>7012874</v>
+        <v>7012805</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2303,22 +2360,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,21 +2388,5463 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137132748</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137132749</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>637635</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7012804</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132749</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137132754</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>637633</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7012934</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132754</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137132720</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79507</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>637898</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7012644</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132720</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137132721</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79507</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>637871</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7012641</v>
+      </c>
+      <c r="S19" t="n">
+        <v>14</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132721</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>119937707</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>OffersjÃ¶n, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>637626</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7012930</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937707</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137124341</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80102</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>637720</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7012872</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124341</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137124352</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>637643</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7012900</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124352</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137124344</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>637677</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7012940</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124344</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137016308</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>637653</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7012948</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016308</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137124338</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>637792</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7012704</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124338</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137124339</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>637711</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7012805</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124339</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137124342</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>637724</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7012872</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124342</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137124343</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>637734</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7012874</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124343</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137124345</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>637672</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7012916</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124345</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137132735</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>637781</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7012711</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132735</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137132752</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>637668</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7012912</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132752</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137132753</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>637653</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7012933</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132753</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137132755</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>637560</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7012941</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132755</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137124346</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>637677</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7012912</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124346</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137124347</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>637685</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7012918</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124347</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118326060</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ljusmon, Ljusmon, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>637736</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7012765</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118326060</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118326208</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sunnersta-Stormyran, Sunnersta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>637768</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7012813</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118326208</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118326344</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ljusmon, Ljusmon, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>637727</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7012895</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118326344</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118326401</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ljusmon, Ljusmon, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>637692</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7012939</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118326401</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>118511426</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Följansbodarna, S om, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>637754</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7012806</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118511426</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>118511429</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Följansbodarna, S om, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>637737</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7012765</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118511429</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137016309</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>637583</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7012906</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1150 plantor inom en cirka 10 meters radie.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016309</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137016310</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>637569</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7012874</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137016310</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137124348</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>637658</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7012887</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124348</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137124351</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>637641</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7012865</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124351</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137124353</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>637601</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7012921</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124353</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137124354</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>637556</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7012944</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124354</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137124371</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>637695</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7012893</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124371</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137132737</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>637747</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7012734</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132737</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137132738</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>637729</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7012748</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132738</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137132740</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>637711</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7012826</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132740</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137132741</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>637727</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7012883</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132741</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137132742</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>637700</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7012894</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132742</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137132743</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98230</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>637678</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7012883</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132743</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137132744</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98230</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>637657</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7012880</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132744</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137132750</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98230</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>637642</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7012856</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132750</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137124326</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79241</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>637879</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7012641</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124326</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137124335</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>637827</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7012677</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124335</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137132745</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>637666</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7012832</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132745</t>
         </is>
       </c>
     </row>
@@ -2365,6 +7864,50 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>137124371</v>
       </c>
       <c r="B48" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>137132737</v>
       </c>
       <c r="B49" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>137132738</v>
       </c>
       <c r="B50" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>137132740</v>
       </c>
       <c r="B51" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>137132741</v>
       </c>
       <c r="B52" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>137132742</v>
       </c>
       <c r="B53" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>137132743</v>
       </c>
       <c r="B54" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>137132744</v>
       </c>
       <c r="B55" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>137132750</v>
       </c>
       <c r="B56" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>137124326</v>
       </c>
       <c r="B57" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>137124335</v>
       </c>
       <c r="B58" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>137132745</v>
       </c>
       <c r="B59" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -5638,7 +5638,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>137124371</v>
       </c>
       <c r="B48" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>137132737</v>
       </c>
       <c r="B49" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>137132738</v>
       </c>
       <c r="B50" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>137132740</v>
       </c>
       <c r="B51" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>137132741</v>
       </c>
       <c r="B52" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>137132742</v>
       </c>
       <c r="B53" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>137132743</v>
       </c>
       <c r="B54" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>137132744</v>
       </c>
       <c r="B55" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>137132750</v>
       </c>
       <c r="B56" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137124371</v>
+        <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6424,7 +6424,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -6433,13 +6437,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>637695</v>
+        <v>637747</v>
       </c>
       <c r="R48" t="n">
-        <v>7012893</v>
+        <v>7012734</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6468,7 +6472,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6478,7 +6482,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6487,33 +6491,34 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137124371</t>
+          <t>https://artportalen.se/Sighting/137132737</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137132737</v>
+        <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6540,7 +6545,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6561,10 +6566,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>637747</v>
+        <v>637729</v>
       </c>
       <c r="R49" t="n">
-        <v>7012734</v>
+        <v>7012748</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6596,7 +6601,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6606,7 +6611,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6633,16 +6638,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132737</t>
+          <t>https://artportalen.se/Sighting/137132738</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137132738</v>
+        <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6669,7 +6674,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6690,10 +6695,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>637729</v>
+        <v>637711</v>
       </c>
       <c r="R50" t="n">
-        <v>7012748</v>
+        <v>7012826</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6725,7 +6730,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6735,7 +6740,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6762,16 +6767,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132738</t>
+          <t>https://artportalen.se/Sighting/137132740</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137132740</v>
+        <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6798,7 +6803,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6819,10 +6824,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>637711</v>
+        <v>637727</v>
       </c>
       <c r="R51" t="n">
-        <v>7012826</v>
+        <v>7012883</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6854,7 +6859,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6864,7 +6869,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6885,22 +6890,22 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132740</t>
+          <t>https://artportalen.se/Sighting/137132741</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137132741</v>
+        <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6927,7 +6932,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>174</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6948,10 +6953,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>637727</v>
+        <v>637700</v>
       </c>
       <c r="R52" t="n">
-        <v>7012883</v>
+        <v>7012894</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6983,7 +6988,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6993,7 +6998,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7014,73 +7019,57 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132741</t>
+          <t>https://artportalen.se/Sighting/137132742</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137132742</v>
+        <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>99374</v>
+        <v>98238</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>637700</v>
+        <v>637678</v>
       </c>
       <c r="R53" t="n">
-        <v>7012894</v>
+        <v>7012883</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7112,7 +7101,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7122,7 +7111,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7131,7 +7120,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7143,22 +7131,22 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132742</t>
+          <t>https://artportalen.se/Sighting/137132743</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137132743</v>
+        <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7190,10 +7178,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>637678</v>
+        <v>637657</v>
       </c>
       <c r="R54" t="n">
-        <v>7012883</v>
+        <v>7012880</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7225,7 +7213,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7235,7 +7223,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7261,16 +7249,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132743</t>
+          <t>https://artportalen.se/Sighting/137132744</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137132744</v>
+        <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7302,10 +7290,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>637657</v>
+        <v>637642</v>
       </c>
       <c r="R55" t="n">
-        <v>7012880</v>
+        <v>7012856</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7337,7 +7325,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7347,7 +7335,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7373,38 +7361,38 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132744</t>
+          <t>https://artportalen.se/Sighting/137132750</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137132750</v>
+        <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>98236</v>
+        <v>79246</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7414,13 +7402,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>637642</v>
+        <v>637879</v>
       </c>
       <c r="R56" t="n">
-        <v>7012856</v>
+        <v>7012641</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7449,7 +7437,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7459,7 +7447,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7474,27 +7462,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132750</t>
+          <t>https://artportalen.se/Sighting/137124326</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137124326</v>
+        <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79243</v>
+        <v>79511</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7502,21 +7490,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>260591</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7526,10 +7514,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>637879</v>
+        <v>637827</v>
       </c>
       <c r="R57" t="n">
-        <v>7012641</v>
+        <v>7012677</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7561,7 +7549,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7571,7 +7559,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7597,16 +7585,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137124326</t>
+          <t>https://artportalen.se/Sighting/137124335</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137124335</v>
+        <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7632,19 +7620,26 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>637827</v>
+        <v>637666</v>
       </c>
       <c r="R58" t="n">
-        <v>7012677</v>
+        <v>7012832</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7673,7 +7668,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7683,7 +7678,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7692,157 +7687,38 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137124335</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>137132745</v>
-      </c>
-      <c r="B59" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>637666</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7012832</v>
-      </c>
-      <c r="S59" t="n">
-        <v>5</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Boteå</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137132745</t>
         </is>
@@ -7907,7 +7783,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>137124344</v>
       </c>
       <c r="B23" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>137016308</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>137124338</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>137124339</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>137124342</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>137124343</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>137124345</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>137132735</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>137132752</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>137132753</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>137132755</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>137124346</v>
       </c>
       <c r="B34" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>137124347</v>
       </c>
       <c r="B35" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>137124344</v>
       </c>
       <c r="B23" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>137016308</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>137124338</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>137124339</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>137124342</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>137124343</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>137124345</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>137132735</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>137132752</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>137132753</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>137132755</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>137124346</v>
       </c>
       <c r="B34" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>137124347</v>
       </c>
       <c r="B35" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -3318,11 +3318,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3438,11 +3434,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3566,16 +3558,8 @@
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3699,11 +3683,7 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3823,11 +3803,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3948,11 +3924,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4073,11 +4045,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4198,11 +4166,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4323,11 +4287,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4448,11 +4408,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4573,11 +4529,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4702,11 +4654,7 @@
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4826,11 +4774,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -6424,11 +6368,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -6553,11 +6493,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -6682,11 +6618,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -6811,11 +6743,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -6940,11 +6868,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -7621,11 +7545,7 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>137124344</v>
       </c>
       <c r="B23" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>137016308</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>137124338</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>137124339</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>137124342</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>137124343</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137124345</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137132735</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>137132752</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137132753</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>137132755</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>137124346</v>
       </c>
       <c r="B34" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137124347</v>
       </c>
       <c r="B35" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>137124344</v>
       </c>
       <c r="B23" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>137016308</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>137124338</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>137124339</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>137124342</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>137124343</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137124345</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137132735</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>137132752</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137132753</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>137132755</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>137124346</v>
       </c>
       <c r="B34" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137124347</v>
       </c>
       <c r="B35" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>137124344</v>
       </c>
       <c r="B23" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>137016308</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>137124338</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>137124339</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>137124342</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>137124343</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137124345</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137132735</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>137132752</v>
       </c>
       <c r="B31" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137132753</v>
       </c>
       <c r="B32" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>137132755</v>
       </c>
       <c r="B33" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>137124346</v>
       </c>
       <c r="B34" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137124347</v>
       </c>
       <c r="B35" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59662-2023 artfynd.xlsx
+++ b/artfynd/A 59662-2023 artfynd.xlsx
@@ -1138,7 +1138,7 @@
         <v>137124325</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137124336</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137124349</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137124350</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>137132734</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137132736</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137132739</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137132746</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137132747</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>137132748</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137132749</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>137132754</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>137132720</v>
       </c>
       <c r="B18" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>137132721</v>
       </c>
       <c r="B19" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>137124341</v>
       </c>
       <c r="B21" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>137124352</v>
       </c>
       <c r="B22" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>137124344</v>
       </c>
       <c r="B23" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>137016308</v>
       </c>
       <c r="B24" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>137124338</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>137124339</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>137124342</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>137124343</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137124345</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137132735</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>137132752</v>
       </c>
       <c r="B31" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137132753</v>
       </c>
       <c r="B32" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>137132755</v>
       </c>
       <c r="B33" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>137124346</v>
       </c>
       <c r="B34" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137124347</v>
       </c>
       <c r="B35" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>137016309</v>
       </c>
       <c r="B42" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>137016310</v>
       </c>
       <c r="B43" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137124348</v>
       </c>
       <c r="B44" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>137124351</v>
       </c>
       <c r="B45" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>137124353</v>
       </c>
       <c r="B46" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>137124354</v>
       </c>
       <c r="B47" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137132737</v>
       </c>
       <c r="B48" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137132738</v>
       </c>
       <c r="B49" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>137132740</v>
       </c>
       <c r="B50" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>137132741</v>
       </c>
       <c r="B51" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>137132742</v>
       </c>
       <c r="B52" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>137132743</v>
       </c>
       <c r="B53" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>137132744</v>
       </c>
       <c r="B54" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>137132750</v>
       </c>
       <c r="B55" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>137124326</v>
       </c>
       <c r="B56" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>137124335</v>
       </c>
       <c r="B57" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>137132745</v>
       </c>
       <c r="B58" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
